--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513089_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513089_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2474</v>
+        <v>4.1027</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9059</v>
+        <v>2.4294</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3415</v>
+        <v>1.6734</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9956</v>
+        <v>1.9791</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5117</v>
+        <v>3.4797</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5161</v>
+        <v>-1.5005</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9455</v>
+        <v>2.8087</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7874</v>
+        <v>1.8563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1581</v>
+        <v>0.9523</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9499</v>
+        <v>-0.8295</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7242</v>
+        <v>1.6234</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6741</v>
+        <v>-2.4529</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6145</v>
+        <v>2.0245</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4809</v>
+        <v>-0.1721</v>
       </c>
       <c r="T2" t="n">
-        <v>0.804</v>
+        <v>0.0379</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6768999999999999</v>
+        <v>-0.2099</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1806</v>
+        <v>1.2834</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1806</v>
+        <v>0.5951</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1899</v>
+        <v>3.1263</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6502</v>
+        <v>4.0033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5397</v>
+        <v>-0.8769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.059</v>
+        <v>2.974</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3315</v>
+        <v>2.6075</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2724</v>
+        <v>0.3665</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8874</v>
+        <v>5.1853</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1366</v>
+        <v>2.3482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7508</v>
+        <v>2.8371</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8283</v>
+        <v>-2.2113</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1949</v>
+        <v>0.2593</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0232</v>
+        <v>-2.4706</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0242</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q3" t="n">
+        <v>-2.0245</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4172</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.0828</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.0242</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.3486</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.7628</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.5859</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-0.2421</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.2421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5839</v>
+        <v>2.7585</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3067</v>
+        <v>2.8769</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2773</v>
+        <v>-0.1184</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9761</v>
+        <v>0.9951</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4923</v>
+        <v>2.5293</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5163</v>
+        <v>-1.5342</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7231</v>
+        <v>1.9949</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8207</v>
+        <v>1.8359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9024</v>
+        <v>0.159</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.747</v>
+        <v>-0.9998</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6716</v>
+        <v>0.6934</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4186</v>
+        <v>-1.6932</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0242</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0485</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7032</v>
+        <v>0.9781</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9825</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7207</v>
+        <v>0.274</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2868</v>
+        <v>1.1902</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5903</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5343</v>
+        <v>2.0785</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6566</v>
+        <v>1.7795</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1223</v>
+        <v>0.299</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9163</v>
+        <v>0.0358</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5732</v>
+        <v>0.317</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3431</v>
+        <v>-0.2812</v>
       </c>
       <c r="J5" t="n">
-        <v>5.052</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2674</v>
+        <v>0.1383</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7846</v>
+        <v>0.7553</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1357</v>
+        <v>-0.8578</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3059</v>
+        <v>0.1787</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4415</v>
+        <v>-1.0365</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6145</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4339</v>
+        <v>1.0123</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0095</v>
+        <v>1.2813</v>
       </c>
       <c r="T5" t="n">
-        <v>0.411</v>
+        <v>0.8858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4205</v>
+        <v>0.3955</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4102</v>
+        <v>1.8362</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0155</v>
+        <v>1.6801</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6052</v>
+        <v>0.156</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3334</v>
+        <v>0.0212</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5795</v>
+        <v>5.1571</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2461</v>
+        <v>-5.136</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0179</v>
+        <v>1.6787</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9388</v>
+        <v>4.3441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.079</v>
+        <v>-2.6654</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6844</v>
+        <v>-1.6576</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6407</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3251</v>
+        <v>-2.4706</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0242</v>
+        <v>2.0245</v>
       </c>
       <c r="S6" t="n">
-        <v>1.101</v>
+        <v>0.7095</v>
       </c>
       <c r="T6" t="n">
-        <v>0.804</v>
+        <v>0.4185</v>
       </c>
       <c r="U6" t="n">
-        <v>0.297</v>
+        <v>0.291</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2421</v>
+        <v>0.5951</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2421</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2608</v>
+        <v>0.6397</v>
       </c>
       <c r="E7" t="n">
-        <v>0.839</v>
+        <v>1.5962</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4218</v>
+        <v>-0.9565</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0196</v>
+        <v>1.3452</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1154</v>
+        <v>3.6156</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.135</v>
+        <v>-2.2704</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5587</v>
+        <v>3.0809</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2521</v>
+        <v>3.0014</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6935</v>
+        <v>0.0795</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5783</v>
+        <v>-1.7358</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8633</v>
+        <v>0.6141</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4415</v>
+        <v>-2.3499</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0485</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>0.15</v>
+        <v>0.3067</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2857</v>
+        <v>0.2888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4357</v>
+        <v>0.0179</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1062</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5903</v>
+        <v>0.2509</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4841</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5162</v>
+        <v>0.3464</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2197</v>
+        <v>2.0009</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7034</v>
+        <v>-1.6546</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3382</v>
+        <v>0.3377</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7236</v>
+        <v>2.7465</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3854</v>
+        <v>-2.4088</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9145</v>
+        <v>2.9631</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8355</v>
+        <v>2.8836</v>
       </c>
       <c r="L8" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5763</v>
+        <v>-2.6254</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1119</v>
+        <v>-0.1371</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4645</v>
+        <v>-2.4883</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5191</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1513</v>
+        <v>-0.0414</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0043</v>
+        <v>-2.828</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0635</v>
+        <v>-0.3193</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0678</v>
+        <v>-2.5088</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6067</v>
+        <v>-1.6357</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7413</v>
+        <v>0.7319</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.348</v>
+        <v>-2.3676</v>
       </c>
       <c r="J9" t="n">
+        <v>0.8524</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2.4881</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.4706</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.8098</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.0245</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2147</v>
+      </c>
+      <c r="S9" t="n">
         <v>0.8077</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.7141</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0935</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-2.4144</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.0272</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-2.4415</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.8194</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2.0485</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2291</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.6024</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.3043</v>
+        <v>0.8529</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2981</v>
+        <v>-0.0452</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8857</v>
+        <v>-3.8738</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4923</v>
+        <v>-1.6776</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3933</v>
+        <v>-2.1962</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6782</v>
+        <v>-2.6777</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4403</v>
+        <v>-0.4351</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2378</v>
+        <v>-2.2425</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.166</v>
+        <v>-1.1218</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9974</v>
+        <v>-0.97</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1685</v>
+        <v>-0.1518</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5122</v>
+        <v>-1.5559</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5571</v>
+        <v>0.5349</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0693</v>
+        <v>-2.0908</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9784</v>
+        <v>0.0186</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4585</v>
+        <v>0.2785</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5199</v>
+        <v>-0.2599</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.8527</v>
+        <v>8.186499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>13.1648</v>
+        <v>14.3694</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.3117</v>
+        <v>-6.183000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3141</v>
+        <v>3.3747</v>
       </c>
       <c r="H11" t="n">
-        <v>20.6282</v>
+        <v>20.7495</v>
       </c>
       <c r="I11" t="n">
-        <v>-17.314</v>
+        <v>-17.3747</v>
       </c>
       <c r="J11" t="n">
-        <v>17.7408</v>
+        <v>18.3358</v>
       </c>
       <c r="K11" t="n">
-        <v>15.7552</v>
+        <v>16.1872</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9854</v>
+        <v>2.1485</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.4265</v>
+        <v>-14.9612</v>
       </c>
       <c r="N11" t="n">
-        <v>4.873</v>
+        <v>4.5622</v>
       </c>
       <c r="O11" t="n">
-        <v>-19.2993</v>
+        <v>-19.5234</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.3151</v>
+        <v>-13.1594</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2665</v>
+        <v>11.135</v>
       </c>
       <c r="S11" t="n">
-        <v>4.71</v>
+        <v>4.9576</v>
       </c>
       <c r="T11" t="n">
-        <v>4.228899999999999</v>
+        <v>4.6185</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4811999999999999</v>
+        <v>0.3391999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8771</v>
+        <v>1.8785</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5101</v>
+        <v>4.5743</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.633</v>
+        <v>-2.6958</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8746</v>
+        <v>3.247</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6476</v>
+        <v>5.9961</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.773</v>
+        <v>-2.7491</v>
       </c>
       <c r="G12" t="n">
-        <v>5.7081</v>
+        <v>5.7263</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7974</v>
+        <v>-0.8098</v>
       </c>
       <c r="I12" t="n">
-        <v>6.5055</v>
+        <v>6.5361</v>
       </c>
       <c r="J12" t="n">
-        <v>8.670199999999999</v>
+        <v>8.7631</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7922</v>
+        <v>0.8284</v>
       </c>
       <c r="L12" t="n">
-        <v>7.878</v>
+        <v>7.9347</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9621</v>
+        <v>-3.0369</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5896</v>
+        <v>-1.6382</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3725</v>
+        <v>-1.3987</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.896</v>
+        <v>-1.5504</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9741</v>
+        <v>-0.7425</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8079</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8436</v>
+        <v>2.2395</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3106</v>
+        <v>2.8527</v>
       </c>
       <c r="F13" t="n">
-        <v>0.533</v>
+        <v>-0.6131</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0892</v>
+        <v>2.0935</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.385</v>
+        <v>-0.8086</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2958</v>
+        <v>2.9021</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1529</v>
+        <v>3.8786</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2046</v>
+        <v>0.7704</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9484</v>
+        <v>3.1081</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2421</v>
+        <v>-1.7851</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5896</v>
+        <v>-1.5791</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3474</v>
+        <v>-0.206</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6145</v>
+        <v>1.8221</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6388</v>
+        <v>1.8221</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3748</v>
+        <v>-0.8687</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8784</v>
+        <v>-0.3376</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4964</v>
+        <v>-0.5311</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0566</v>
+        <v>-0.8074</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3601</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5153</v>
+        <v>2.019</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1538</v>
+        <v>2.109</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6385</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1119</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-2.5483</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8846</v>
+        <v>2.643</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8328</v>
+        <v>1.0054</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7611</v>
+        <v>-0.9101</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0717</v>
+        <v>1.9155</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7208</v>
+        <v>-0.9107</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5338</v>
+        <v>-1.6382</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1871</v>
+        <v>0.7275</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8436</v>
+        <v>1.6196</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8436</v>
+        <v>1.6196</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6257</v>
+        <v>-1.0174</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9825</v>
+        <v>-0.3376</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6432</v>
+        <v>-0.6798</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8145</v>
+        <v>1.3221</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6965</v>
+        <v>1.4411</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.402</v>
+        <v>-0.0499</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4013</v>
+        <v>0.0595</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007</v>
+        <v>-0.1094</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1141</v>
+        <v>-0.0809</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5147</v>
+        <v>-1.365</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6288</v>
+        <v>1.2841</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9611</v>
+        <v>1.2274</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9252</v>
+        <v>0.2732</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8862</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.847</v>
+        <v>-1.3082</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5896</v>
+        <v>-1.6382</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7426</v>
+        <v>0.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6388</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6555</v>
+        <v>0.4819</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9825</v>
+        <v>0.5327</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.673</v>
+        <v>-0.0508</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3046</v>
+        <v>-1.0583</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4227</v>
+        <v>-0.6883</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1181</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2436</v>
+        <v>-0.4115</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5528</v>
+        <v>1.4481</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7963</v>
+        <v>-1.8596</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9813</v>
+        <v>-0.2517</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2937</v>
+        <v>-5.0989</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3124</v>
+        <v>4.8472</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5347</v>
+        <v>1.4102</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4532</v>
+        <v>-2.9863</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9879</v>
+        <v>4.3965</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.516</v>
+        <v>-1.6619</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8405</v>
+        <v>-2.1126</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3245</v>
+        <v>0.4507</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4097</v>
+        <v>1.6196</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S16" t="n">
-        <v>1.328</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0666</v>
+        <v>0.0379</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7385</v>
+        <v>-0.6271</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6309</v>
+        <v>-1.8929</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4288</v>
+        <v>-1.0552</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0597</v>
+        <v>-0.8377</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2538</v>
+        <v>-2.4245</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.0788</v>
+        <v>-3.8542</v>
       </c>
       <c r="I17" t="n">
-        <v>4.825</v>
+        <v>1.4297</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3458</v>
+        <v>-1.1174</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.0154</v>
+        <v>-2.3733</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3612</v>
+        <v>1.2559</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5995</v>
+        <v>-1.3071</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0634</v>
+        <v>-1.481</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4639</v>
+        <v>0.1738</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6388</v>
+        <v>0.8098</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6388</v>
+        <v>0.8098</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8353</v>
+        <v>-0.0273</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.917</v>
+        <v>0.0621</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9183</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9655</v>
+        <v>-2.5926</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1071</v>
+        <v>-0.6955</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-1.8971</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.422</v>
+        <v>-0.9681</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.8466</v>
+        <v>-2.2742</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4246</v>
+        <v>1.3061</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1572</v>
+        <v>0.6145</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3967</v>
+        <v>-0.3793</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2395</v>
+        <v>0.9939</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2647</v>
+        <v>-1.5826</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4499</v>
+        <v>-1.8949</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1852</v>
+        <v>0.3122</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8194</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8194</v>
+        <v>1.6196</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1208</v>
+        <v>-0.0294</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0501</v>
+        <v>0.7144</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.171</v>
+        <v>-0.7439</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6538</v>
+        <v>-2.7266</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6188</v>
+        <v>-1.5291</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.035</v>
+        <v>-1.1975</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7264</v>
+        <v>-1.7256</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.824</v>
+        <v>-1.8244</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0388</v>
+        <v>-0.0008</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1572</v>
+        <v>1.1846</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1959</v>
+        <v>-1.1854</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6876</v>
+        <v>-1.7248</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0596</v>
+        <v>-1.0859</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.628</v>
+        <v>-0.639</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5377</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3121</v>
+        <v>0.3183</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3173</v>
+        <v>0.2194</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2333</v>
+        <v>-3.6025</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2396</v>
+        <v>-1.403</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9937</v>
+        <v>-2.1996</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3688</v>
+        <v>-2.3954</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2357</v>
+        <v>-2.2526</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1331</v>
+        <v>-0.1428</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5647</v>
+        <v>-0.5498</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3155</v>
+        <v>-1.3052</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7508</v>
+        <v>0.7553</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8041</v>
+        <v>-1.8455</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9203</v>
+        <v>-0.9474</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1066</v>
+        <v>-0.4581</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1073</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2139</v>
+        <v>-0.3663</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7613</v>
+        <v>-4.0957</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2177</v>
+        <v>-1.5996</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5436</v>
+        <v>-2.4962</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4068</v>
+        <v>-3.443</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8012</v>
+        <v>-1.8365</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6056</v>
+        <v>-1.6065</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3102</v>
+        <v>-0.2702</v>
       </c>
       <c r="K21" t="n">
-        <v>0.318</v>
+        <v>0.3352</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6282</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0966</v>
+        <v>-3.1728</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1192</v>
+        <v>-2.1717</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9774</v>
+        <v>-1.0011</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8025</v>
+        <v>-1.1165</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0396</v>
+        <v>-0.4951</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7629</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0625</v>
+        <v>1.0712</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.852900000000001</v>
+        <v>-7.866200000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>5.311699999999998</v>
+        <v>6.183000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.1645</v>
+        <v>-14.0492</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3142</v>
+        <v>-3.374699999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-20.6282</v>
+        <v>-20.7493</v>
       </c>
       <c r="I22" t="n">
-        <v>17.314</v>
+        <v>17.3746</v>
       </c>
       <c r="J22" t="n">
-        <v>14.4266</v>
+        <v>14.961</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.8729</v>
+        <v>-4.5624</v>
       </c>
       <c r="L22" t="n">
-        <v>19.2996</v>
+        <v>19.5233</v>
       </c>
       <c r="M22" t="n">
-        <v>-17.7405</v>
+        <v>-18.3356</v>
       </c>
       <c r="N22" t="n">
-        <v>-15.7555</v>
+        <v>-16.1872</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9852</v>
+        <v>-2.1487</v>
       </c>
       <c r="P22" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q22" t="n">
-        <v>-11.2666</v>
+        <v>-11.1349</v>
       </c>
       <c r="R22" t="n">
-        <v>13.3151</v>
+        <v>13.1594</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.7101</v>
+        <v>-4.6374</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4812000000000001</v>
+        <v>-0.3391999999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.229</v>
+        <v>-4.2984</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8771</v>
+        <v>-1.8786</v>
       </c>
       <c r="W22" t="n">
-        <v>2.633</v>
+        <v>2.6958</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.5102</v>
+        <v>-4.574299999999999</v>
       </c>
     </row>
   </sheetData>
